--- a/public/templates/skills_template.xlsx
+++ b/public/templates/skills_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Skill Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +62,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,159 +438,159 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="38" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="37" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Engineer Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Orbit ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fab</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Wafer Size</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Tool Type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t># of Tools</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Previous Process Startup Experience</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Previous CM/PM Experience</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Ready for Primary Role</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Selvaganesh Nagarathinam Rajagopalchettiar</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E150</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Selvaganesh Nagarathinam</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ORB-001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Rapidus</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>300mm</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>SENSAI - Akara</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2025-01-13</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>2025-04-13</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Tier 1 Secondary</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Chamber startup training completed</t>
         </is>

--- a/public/templates/skills_template.xlsx
+++ b/public/templates/skills_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,29 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -62,14 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,164 +413,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="39" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="38" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Engineer Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>skill_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Orbit ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fab</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Wafer Size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tool Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t># of Tools</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Previous Process Startup Experience</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Previous CM/PM Experience</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Ready for Primary Role</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Selvaganesh Nagarathinam</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>ORB-001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Rapidus</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>300mm</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>SENSAI - Akara</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Tier 1 Secondary</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Chamber startup training completed</t>
         </is>
       </c>
     </row>
